--- a/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256034695617408</v>
+        <v>1.248308341184986</v>
       </c>
       <c r="C3" t="n">
-        <v>4.650565273265317</v>
+        <v>4.634621690548349</v>
       </c>
       <c r="D3" t="n">
-        <v>6.105906309419859</v>
+        <v>6.090964109361222</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01250627830258</v>
+        <v>11.97389414109456</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.38312097029339</v>
+        <v>1.362098559148889</v>
       </c>
       <c r="C4" t="n">
-        <v>5.207638262260939</v>
+        <v>5.136604228101189</v>
       </c>
       <c r="D4" t="n">
-        <v>6.325768377264418</v>
+        <v>6.429638063747904</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91652760981875</v>
+        <v>12.92834085099798</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.557684006119899</v>
+        <v>1.521178157278604</v>
       </c>
       <c r="C5" t="n">
-        <v>5.931883600688711</v>
+        <v>5.769012041893683</v>
       </c>
       <c r="D5" t="n">
-        <v>6.627894783580502</v>
+        <v>6.781323440753803</v>
       </c>
       <c r="E5" t="n">
-        <v>14.11746239038911</v>
+        <v>14.07151363992609</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.744961468648302</v>
+        <v>1.702712011080808</v>
       </c>
       <c r="C6" t="n">
-        <v>6.813398041237909</v>
+        <v>6.553001087582129</v>
       </c>
       <c r="D6" t="n">
-        <v>7.039222625892277</v>
+        <v>7.116745119894689</v>
       </c>
       <c r="E6" t="n">
-        <v>15.59758213577849</v>
+        <v>15.37245821855763</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.956501815514189</v>
+        <v>1.925795013203844</v>
       </c>
       <c r="C7" t="n">
-        <v>7.884989186289681</v>
+        <v>7.455618377539686</v>
       </c>
       <c r="D7" t="n">
-        <v>7.409706889770928</v>
+        <v>7.555006305292288</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2511978915748</v>
+        <v>16.93641969603582</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.178270451578911</v>
+        <v>1.194172898139535</v>
       </c>
       <c r="C8" t="n">
-        <v>5.563616027230927</v>
+        <v>5.121791202104504</v>
       </c>
       <c r="D8" t="n">
-        <v>5.618072361495332</v>
+        <v>5.905194355858876</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35995884030517</v>
+        <v>12.22115845610291</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.465695775588276</v>
+        <v>1.509022230573574</v>
       </c>
       <c r="C9" t="n">
-        <v>6.947873047647199</v>
+        <v>6.300963046093678</v>
       </c>
       <c r="D9" t="n">
-        <v>6.044946155928285</v>
+        <v>6.503242157083925</v>
       </c>
       <c r="E9" t="n">
-        <v>14.45851497916376</v>
+        <v>14.31322743375118</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.774750499068919</v>
+        <v>1.834525042043288</v>
       </c>
       <c r="C10" t="n">
-        <v>8.518902327686122</v>
+        <v>7.638778574897397</v>
       </c>
       <c r="D10" t="n">
-        <v>6.496899767978858</v>
+        <v>7.175283866218337</v>
       </c>
       <c r="E10" t="n">
-        <v>16.7905525947339</v>
+        <v>16.64858748315902</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.08466257706226</v>
+        <v>2.158321996701707</v>
       </c>
       <c r="C11" t="n">
-        <v>10.20448037377198</v>
+        <v>9.086444031734738</v>
       </c>
       <c r="D11" t="n">
-        <v>6.961013241533209</v>
+        <v>7.816624890128199</v>
       </c>
       <c r="E11" t="n">
-        <v>19.25015619236745</v>
+        <v>19.06139091856464</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.389985294705055</v>
+        <v>2.478396575930564</v>
       </c>
       <c r="C12" t="n">
-        <v>11.95086023133044</v>
+        <v>10.57031852630783</v>
       </c>
       <c r="D12" t="n">
-        <v>7.438987218696046</v>
+        <v>8.44918412131949</v>
       </c>
       <c r="E12" t="n">
-        <v>21.77983274473154</v>
+        <v>21.49789922355789</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.678326171955804</v>
+        <v>2.782467452932078</v>
       </c>
       <c r="C13" t="n">
-        <v>13.73686284412986</v>
+        <v>12.04422933861471</v>
       </c>
       <c r="D13" t="n">
-        <v>7.973473382735119</v>
+        <v>9.043940937021187</v>
       </c>
       <c r="E13" t="n">
-        <v>24.38866239882078</v>
+        <v>23.87063772856797</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.538860073975748</v>
+        <v>1.590765075099277</v>
       </c>
       <c r="C14" t="n">
-        <v>9.556773939605364</v>
+        <v>8.382299343537861</v>
       </c>
       <c r="D14" t="n">
-        <v>6.053534884202172</v>
+        <v>6.878428757741471</v>
       </c>
       <c r="E14" t="n">
-        <v>17.14916889778328</v>
+        <v>16.85149317637861</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.564032085112636</v>
+        <v>1.62598036525061</v>
       </c>
       <c r="C15" t="n">
-        <v>10.38448542905585</v>
+        <v>8.946578471507802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.059818069509353</v>
+        <v>6.995109472391203</v>
       </c>
       <c r="E15" t="n">
-        <v>18.00833558367784</v>
+        <v>17.56766830914961</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.800662734267245</v>
+        <v>1.882373595691707</v>
       </c>
       <c r="C16" t="n">
-        <v>12.2538312327122</v>
+        <v>10.47330414385906</v>
       </c>
       <c r="D16" t="n">
-        <v>6.542121264174683</v>
+        <v>7.579033371923122</v>
       </c>
       <c r="E16" t="n">
-        <v>20.59661523115413</v>
+        <v>19.93471111147389</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.435099159113903</v>
+        <v>1.512117266512065</v>
       </c>
       <c r="C17" t="n">
-        <v>11.2267071495751</v>
+        <v>9.570341692878056</v>
       </c>
       <c r="D17" t="n">
-        <v>6.08128889180123</v>
+        <v>7.106459297006877</v>
       </c>
       <c r="E17" t="n">
-        <v>18.74309520049024</v>
+        <v>18.188918256397</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.622171184158132</v>
+        <v>1.726403337918016</v>
       </c>
       <c r="C18" t="n">
-        <v>13.02518058646188</v>
+        <v>11.10730699378461</v>
       </c>
       <c r="D18" t="n">
-        <v>6.491639797222311</v>
+        <v>7.609693352726749</v>
       </c>
       <c r="E18" t="n">
-        <v>21.13899156784232</v>
+        <v>20.44340368442937</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.618136201093678</v>
+        <v>1.73449293900101</v>
       </c>
       <c r="C19" t="n">
-        <v>13.84414470386752</v>
+        <v>11.839523884043</v>
       </c>
       <c r="D19" t="n">
-        <v>6.582117665645697</v>
+        <v>7.768353599210077</v>
       </c>
       <c r="E19" t="n">
-        <v>22.0443985706069</v>
+        <v>21.34237042225409</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.787585854846677</v>
+        <v>1.935839575664988</v>
       </c>
       <c r="C20" t="n">
-        <v>15.81482650555623</v>
+        <v>13.64411360912723</v>
       </c>
       <c r="D20" t="n">
-        <v>6.996906070689975</v>
+        <v>8.299263122712668</v>
       </c>
       <c r="E20" t="n">
-        <v>24.59931843109288</v>
+        <v>23.87921630750489</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.057636801785089</v>
+        <v>1.151521334742211</v>
       </c>
       <c r="C21" t="n">
-        <v>11.51180668288838</v>
+        <v>10.08868484576629</v>
       </c>
       <c r="D21" t="n">
-        <v>5.847387501264427</v>
+        <v>6.973265585971713</v>
       </c>
       <c r="E21" t="n">
-        <v>18.41683098593789</v>
+        <v>18.21347176648021</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248308341184986</v>
+        <v>1.261434307990765</v>
       </c>
       <c r="C3" t="n">
-        <v>4.634621690548349</v>
+        <v>4.693477465417945</v>
       </c>
       <c r="D3" t="n">
-        <v>6.090964109361222</v>
+        <v>6.058586070075162</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97389414109456</v>
+        <v>12.01349784348387</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.362098559148889</v>
+        <v>1.402932468986594</v>
       </c>
       <c r="C4" t="n">
-        <v>5.136604228101189</v>
+        <v>5.322285869275462</v>
       </c>
       <c r="D4" t="n">
-        <v>6.429638063747904</v>
+        <v>6.280244716221023</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92834085099798</v>
+        <v>13.00546305448308</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.521178157278604</v>
+        <v>1.590712578307327</v>
       </c>
       <c r="C5" t="n">
-        <v>5.769012041893683</v>
+        <v>6.180033173238393</v>
       </c>
       <c r="D5" t="n">
-        <v>6.781323440753803</v>
+        <v>6.540613822033484</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07151363992609</v>
+        <v>14.3113595735792</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.702712011080808</v>
+        <v>1.793815873467402</v>
       </c>
       <c r="C6" t="n">
-        <v>6.553001087582129</v>
+        <v>7.231357881643883</v>
       </c>
       <c r="D6" t="n">
-        <v>7.116745119894689</v>
+        <v>6.816096576173529</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37245821855763</v>
+        <v>15.84127033128481</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.925795013203844</v>
+        <v>2.01284332022262</v>
       </c>
       <c r="C7" t="n">
-        <v>7.455618377539686</v>
+        <v>8.419281578902355</v>
       </c>
       <c r="D7" t="n">
-        <v>7.555006305292288</v>
+        <v>7.180471741308882</v>
       </c>
       <c r="E7" t="n">
-        <v>16.93641969603582</v>
+        <v>17.61259664043386</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.194172898139535</v>
+        <v>1.206858699133815</v>
       </c>
       <c r="C8" t="n">
-        <v>5.121791202104504</v>
+        <v>5.998659266535551</v>
       </c>
       <c r="D8" t="n">
-        <v>5.905194355858876</v>
+        <v>5.385698662327786</v>
       </c>
       <c r="E8" t="n">
-        <v>12.22115845610291</v>
+        <v>12.59121662799715</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.509022230573574</v>
+        <v>1.490491841171254</v>
       </c>
       <c r="C9" t="n">
-        <v>6.300963046093678</v>
+        <v>7.435934977415871</v>
       </c>
       <c r="D9" t="n">
-        <v>6.503242157083925</v>
+        <v>5.874191071028175</v>
       </c>
       <c r="E9" t="n">
-        <v>14.31322743375118</v>
+        <v>14.8006178896153</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.834525042043288</v>
+        <v>1.786291678679141</v>
       </c>
       <c r="C10" t="n">
-        <v>7.638778574897397</v>
+        <v>9.061349523441967</v>
       </c>
       <c r="D10" t="n">
-        <v>7.175283866218337</v>
+        <v>6.317977505900643</v>
       </c>
       <c r="E10" t="n">
-        <v>16.64858748315902</v>
+        <v>17.16561870802175</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.158321996701707</v>
+        <v>2.079668428842869</v>
       </c>
       <c r="C11" t="n">
-        <v>9.086444031734738</v>
+        <v>10.7963921693004</v>
       </c>
       <c r="D11" t="n">
-        <v>7.816624890128199</v>
+        <v>6.730649090326921</v>
       </c>
       <c r="E11" t="n">
-        <v>19.06139091856464</v>
+        <v>19.60670968847019</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.478396575930564</v>
+        <v>2.369626773017333</v>
       </c>
       <c r="C12" t="n">
-        <v>10.57031852630783</v>
+        <v>12.62150398559054</v>
       </c>
       <c r="D12" t="n">
-        <v>8.44918412131949</v>
+        <v>7.090486028499274</v>
       </c>
       <c r="E12" t="n">
-        <v>21.49789922355789</v>
+        <v>22.08161678710714</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.782467452932078</v>
+        <v>2.653898515289314</v>
       </c>
       <c r="C13" t="n">
-        <v>12.04422933861471</v>
+        <v>14.50503193291517</v>
       </c>
       <c r="D13" t="n">
-        <v>9.043940937021187</v>
+        <v>7.476969444666079</v>
       </c>
       <c r="E13" t="n">
-        <v>23.87063772856797</v>
+        <v>24.63589989287057</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.590765075099277</v>
+        <v>1.538290660307285</v>
       </c>
       <c r="C14" t="n">
-        <v>8.382299343537861</v>
+        <v>10.17668870997497</v>
       </c>
       <c r="D14" t="n">
-        <v>6.878428757741471</v>
+        <v>5.699771916453877</v>
       </c>
       <c r="E14" t="n">
-        <v>16.85149317637861</v>
+        <v>17.41475128673613</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.62598036525061</v>
+        <v>1.565661786301686</v>
       </c>
       <c r="C15" t="n">
-        <v>8.946578471507802</v>
+        <v>11.0757045351849</v>
       </c>
       <c r="D15" t="n">
-        <v>6.995109472391203</v>
+        <v>5.634770400955696</v>
       </c>
       <c r="E15" t="n">
-        <v>17.56766830914961</v>
+        <v>18.27613672244228</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.882373595691707</v>
+        <v>1.800063868167654</v>
       </c>
       <c r="C16" t="n">
-        <v>10.47330414385906</v>
+        <v>13.14157659427738</v>
       </c>
       <c r="D16" t="n">
-        <v>7.579033371923122</v>
+        <v>6.026497552427215</v>
       </c>
       <c r="E16" t="n">
-        <v>19.93471111147389</v>
+        <v>20.96813801487225</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.512117266512065</v>
+        <v>1.434097776455571</v>
       </c>
       <c r="C17" t="n">
-        <v>9.570341692878056</v>
+        <v>12.09391434916744</v>
       </c>
       <c r="D17" t="n">
-        <v>7.106459297006877</v>
+        <v>5.539747040661647</v>
       </c>
       <c r="E17" t="n">
-        <v>18.188918256397</v>
+        <v>19.06775916628466</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.726403337918016</v>
+        <v>1.61607453091476</v>
       </c>
       <c r="C18" t="n">
-        <v>11.10730699378461</v>
+        <v>14.18058964211291</v>
       </c>
       <c r="D18" t="n">
-        <v>7.609693352726749</v>
+        <v>5.863380171366608</v>
       </c>
       <c r="E18" t="n">
-        <v>20.44340368442937</v>
+        <v>21.66004434439428</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.73449293900101</v>
+        <v>1.602320245578262</v>
       </c>
       <c r="C19" t="n">
-        <v>11.839523884043</v>
+        <v>15.20529862589756</v>
       </c>
       <c r="D19" t="n">
-        <v>7.768353599210077</v>
+        <v>5.88948484282253</v>
       </c>
       <c r="E19" t="n">
-        <v>21.34237042225409</v>
+        <v>22.69710371429835</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.935839575664988</v>
+        <v>1.757514922665598</v>
       </c>
       <c r="C20" t="n">
-        <v>13.64411360912723</v>
+        <v>17.43769473058438</v>
       </c>
       <c r="D20" t="n">
-        <v>8.299263122712668</v>
+        <v>6.256413047284776</v>
       </c>
       <c r="E20" t="n">
-        <v>23.87921630750489</v>
+        <v>25.45162270053475</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.151521334742211</v>
+        <v>1.030196953451391</v>
       </c>
       <c r="C21" t="n">
-        <v>10.08868484576629</v>
+        <v>12.77312668087355</v>
       </c>
       <c r="D21" t="n">
-        <v>6.973265585971713</v>
+        <v>5.182606860810743</v>
       </c>
       <c r="E21" t="n">
-        <v>18.21347176648021</v>
+        <v>18.98593049513568</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_31_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261434307990765</v>
+        <v>2.597723582274674</v>
       </c>
       <c r="C3" t="n">
-        <v>4.693477465417945</v>
+        <v>7.702760204445853</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058586070075162</v>
+        <v>8.125982457970526</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01349784348387</v>
+        <v>18.42646624469105</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.402932468986594</v>
+        <v>1.08467225403265</v>
       </c>
       <c r="C4" t="n">
-        <v>5.322285869275462</v>
+        <v>4.543559305918714</v>
       </c>
       <c r="D4" t="n">
-        <v>6.280244716221023</v>
+        <v>5.731669428561498</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00546305448308</v>
+        <v>11.35990098851286</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.590712578307327</v>
+        <v>1.200325586522389</v>
       </c>
       <c r="C5" t="n">
-        <v>6.180033173238393</v>
+        <v>5.269181268263815</v>
       </c>
       <c r="D5" t="n">
-        <v>6.540613822033484</v>
+        <v>6.11751845468731</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3113595735792</v>
+        <v>12.58702530947352</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.793815873467402</v>
+        <v>1.326266761012859</v>
       </c>
       <c r="C6" t="n">
-        <v>7.231357881643883</v>
+        <v>6.229486344115323</v>
       </c>
       <c r="D6" t="n">
-        <v>6.816096576173529</v>
+        <v>6.477393693852809</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84127033128481</v>
+        <v>14.03314679898099</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.01284332022262</v>
+        <v>1.453333950698629</v>
       </c>
       <c r="C7" t="n">
-        <v>8.419281578902355</v>
+        <v>7.351975431322651</v>
       </c>
       <c r="D7" t="n">
-        <v>7.180471741308882</v>
+        <v>6.878222860691494</v>
       </c>
       <c r="E7" t="n">
-        <v>17.61259664043386</v>
+        <v>15.68353224271277</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.206858699133815</v>
+        <v>1.58567380446351</v>
       </c>
       <c r="C8" t="n">
-        <v>5.998659266535551</v>
+        <v>8.650819995846712</v>
       </c>
       <c r="D8" t="n">
-        <v>5.385698662327786</v>
+        <v>7.276822976112144</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59121662799715</v>
+        <v>17.51331677642236</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.490491841171254</v>
+        <v>1.710589136296557</v>
       </c>
       <c r="C9" t="n">
-        <v>7.435934977415871</v>
+        <v>10.06447383094819</v>
       </c>
       <c r="D9" t="n">
-        <v>5.874191071028175</v>
+        <v>7.681812083501203</v>
       </c>
       <c r="E9" t="n">
-        <v>14.8006178896153</v>
+        <v>19.45687505074595</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.786291678679141</v>
+        <v>1.064361773559179</v>
       </c>
       <c r="C10" t="n">
-        <v>9.061349523441967</v>
+        <v>7.311428582699525</v>
       </c>
       <c r="D10" t="n">
-        <v>6.317977505900643</v>
+        <v>6.054526449383462</v>
       </c>
       <c r="E10" t="n">
-        <v>17.16561870802175</v>
+        <v>14.43031680564217</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.079668428842869</v>
+        <v>1.000371458196372</v>
       </c>
       <c r="C11" t="n">
-        <v>10.7963921693004</v>
+        <v>7.878819850891928</v>
       </c>
       <c r="D11" t="n">
-        <v>6.730649090326921</v>
+        <v>5.911152014655258</v>
       </c>
       <c r="E11" t="n">
-        <v>19.60670968847019</v>
+        <v>14.79034332374356</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.369626773017333</v>
+        <v>1.080285721322063</v>
       </c>
       <c r="C12" t="n">
-        <v>12.62150398559054</v>
+        <v>9.364930620718495</v>
       </c>
       <c r="D12" t="n">
-        <v>7.090486028499274</v>
+        <v>6.283008592592823</v>
       </c>
       <c r="E12" t="n">
-        <v>22.08161678710714</v>
+        <v>16.72822493463338</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.653898515289314</v>
+        <v>0.8513421566917067</v>
       </c>
       <c r="C13" t="n">
-        <v>14.50503193291517</v>
+        <v>8.915476704237262</v>
       </c>
       <c r="D13" t="n">
-        <v>7.476969444666079</v>
+        <v>5.72134091351618</v>
       </c>
       <c r="E13" t="n">
-        <v>24.63589989287057</v>
+        <v>15.48815977444515</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.538290660307285</v>
+        <v>0.9233828032293375</v>
       </c>
       <c r="C14" t="n">
-        <v>10.17668870997497</v>
+        <v>10.46558760690368</v>
       </c>
       <c r="D14" t="n">
-        <v>5.699771916453877</v>
+        <v>6.05280839090103</v>
       </c>
       <c r="E14" t="n">
-        <v>17.41475128673613</v>
+        <v>17.44177880103405</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.565661786301686</v>
+        <v>0.8980144425516</v>
       </c>
       <c r="C15" t="n">
-        <v>11.0757045351849</v>
+        <v>11.33287334631235</v>
       </c>
       <c r="D15" t="n">
-        <v>5.634770400955696</v>
+        <v>6.085274787480472</v>
       </c>
       <c r="E15" t="n">
-        <v>18.27613672244228</v>
+        <v>18.31616257634442</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.800063868167654</v>
+        <v>0.9806775992491814</v>
       </c>
       <c r="C16" t="n">
-        <v>13.14157659427738</v>
+        <v>13.22852017096548</v>
       </c>
       <c r="D16" t="n">
-        <v>6.026497552427215</v>
+        <v>6.453911232948107</v>
       </c>
       <c r="E16" t="n">
-        <v>20.96813801487225</v>
+        <v>20.66310900316276</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.434097776455571</v>
+        <v>0.5865058959940871</v>
       </c>
       <c r="C17" t="n">
-        <v>12.09391434916744</v>
+        <v>9.88949805405165</v>
       </c>
       <c r="D17" t="n">
-        <v>5.539747040661647</v>
+        <v>5.34405527077413</v>
       </c>
       <c r="E17" t="n">
-        <v>19.06775916628466</v>
+        <v>15.82005922081987</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.61607453091476</v>
+        <v>0.4619024773710819</v>
       </c>
       <c r="C18" t="n">
-        <v>14.18058964211291</v>
+        <v>8.866526763703517</v>
       </c>
       <c r="D18" t="n">
-        <v>5.863380171366608</v>
+        <v>4.840575778128196</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66004434439428</v>
+        <v>14.16900501920279</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.602320245578262</v>
+        <v>0.5382333613762714</v>
       </c>
       <c r="C19" t="n">
-        <v>15.20529862589756</v>
+        <v>11.01332428605706</v>
       </c>
       <c r="D19" t="n">
-        <v>5.88948484282253</v>
+        <v>5.315574769873931</v>
       </c>
       <c r="E19" t="n">
-        <v>22.69710371429835</v>
+        <v>16.86713241730726</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.757514922665598</v>
+        <v>0.6067888035638261</v>
       </c>
       <c r="C20" t="n">
-        <v>17.43769473058438</v>
+        <v>13.23514696796914</v>
       </c>
       <c r="D20" t="n">
-        <v>6.256413047284776</v>
+        <v>5.733858196745326</v>
       </c>
       <c r="E20" t="n">
-        <v>25.45162270053475</v>
+        <v>19.57579396827829</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.030196953451391</v>
+        <v>0.6648689977470674</v>
       </c>
       <c r="C21" t="n">
-        <v>12.77312668087355</v>
+        <v>15.44746633210412</v>
       </c>
       <c r="D21" t="n">
-        <v>5.182606860810743</v>
+        <v>6.157050362137957</v>
       </c>
       <c r="E21" t="n">
-        <v>18.98593049513568</v>
+        <v>22.26938569198914</v>
       </c>
     </row>
   </sheetData>
